--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486456_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486456_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.7747</v>
+        <v>2.691</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7595</v>
+        <v>0.0457</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0152</v>
+        <v>2.6453</v>
       </c>
       <c r="G2" t="n">
         <v>0.7725</v>
@@ -610,13 +610,13 @@
         <v>2.3926</v>
       </c>
       <c r="S2" t="n">
-        <v>1.0224</v>
+        <v>-0.0613</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5997</v>
+        <v>-0.1142</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4227</v>
+        <v>0.0529</v>
       </c>
       <c r="V2" t="n">
         <v>-0.1952</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1409</v>
+        <v>1.631</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5555</v>
+        <v>-0.8090000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5854</v>
+        <v>2.44</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2825</v>
+        <v>4.1424</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7511</v>
+        <v>3.9631</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.0336</v>
+        <v>0.1793</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.9262</v>
+        <v>4.1035</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6205000000000001</v>
+        <v>4.3314</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.5467</v>
+        <v>-0.2279</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3563</v>
+        <v>0.0389</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1306</v>
+        <v>-0.3683</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4869</v>
+        <v>0.4072</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2175</v>
+        <v>-4.5676</v>
       </c>
       <c r="R3" t="n">
-        <v>0.435</v>
+        <v>3.2626</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8361</v>
+        <v>-0.4461</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6992</v>
+        <v>-0.3449</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1369</v>
+        <v>-0.1013</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3698</v>
+        <v>-0.7602</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3698</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2995</v>
+        <v>0.4875</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6165</v>
+        <v>0.5544</v>
       </c>
       <c r="F4" t="n">
-        <v>1.916</v>
+        <v>-0.067</v>
       </c>
       <c r="G4" t="n">
-        <v>4.1424</v>
+        <v>2.6537</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9631</v>
+        <v>1.7031</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1793</v>
+        <v>0.9506</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1035</v>
+        <v>2.5949</v>
       </c>
       <c r="K4" t="n">
-        <v>4.3314</v>
+        <v>2.5184</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.2279</v>
+        <v>0.0765</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0389</v>
+        <v>0.0588</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3683</v>
+        <v>-0.8153</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4072</v>
+        <v>0.8741</v>
       </c>
       <c r="P4" t="n">
+        <v>2.1751</v>
+      </c>
+      <c r="Q4" t="n">
         <v>-1.305</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-4.5676</v>
-      </c>
       <c r="R4" t="n">
-        <v>3.2626</v>
+        <v>3.4801</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7777</v>
+        <v>-0.7562</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1524</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6252</v>
+        <v>-0.0207</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7602</v>
+        <v>-3.5851</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.7602</v>
+        <v>-3.5851</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2824</v>
+        <v>0.2688</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.9202</v>
+        <v>-1.9548</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2026</v>
+        <v>2.2236</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.434</v>
+        <v>1.8289</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4355</v>
+        <v>1.6942</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.9985000000000001</v>
+        <v>0.1347</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.1772</v>
+        <v>1.6226</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6871</v>
+        <v>1.448</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.4901</v>
+        <v>0.1745</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2567</v>
+        <v>0.2063</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7484</v>
+        <v>0.2461</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4916</v>
+        <v>-0.0399</v>
       </c>
       <c r="P5" t="n">
-        <v>2.1751</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.435</v>
+        <v>-4.3501</v>
       </c>
       <c r="R5" t="n">
-        <v>2.6101</v>
+        <v>1.9576</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7158</v>
+        <v>-0.1229</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1334</v>
+        <v>-0.1826</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8492</v>
+        <v>0.0598</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1745</v>
+        <v>0.9554</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.1745</v>
+        <v>0.9554</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2194</v>
+        <v>0.1042</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1939</v>
+        <v>-0.4503</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0255</v>
+        <v>0.5545</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6537</v>
+        <v>-1.2825</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7031</v>
+        <v>0.7511</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9506</v>
+        <v>-2.0336</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5949</v>
+        <v>-0.9262</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5184</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0765</v>
+        <v>-1.5467</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0588</v>
+        <v>-0.3563</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8153</v>
+        <v>0.1306</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8741</v>
+        <v>-0.4869</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1751</v>
+        <v>0.2175</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R6" t="n">
-        <v>3.4801</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0242</v>
+        <v>0.7994</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0959</v>
+        <v>0.6934</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0717</v>
+        <v>0.106</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.5851</v>
+        <v>0.3698</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-3.5851</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4578</v>
+        <v>-0.1616</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6506</v>
+        <v>-2.9634</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1928</v>
+        <v>2.8019</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8289</v>
+        <v>-2.434</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6942</v>
+        <v>-1.4355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1347</v>
+        <v>-0.9985000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6226</v>
+        <v>-2.1772</v>
       </c>
       <c r="K7" t="n">
-        <v>1.448</v>
+        <v>-0.6871</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1745</v>
+        <v>-1.4901</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2063</v>
+        <v>-0.2567</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2461</v>
+        <v>-0.7484</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0399</v>
+        <v>0.4916</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.3926</v>
+        <v>2.1751</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.3501</v>
+        <v>-0.435</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>2.6101</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8495</v>
+        <v>0.2719</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8784</v>
+        <v>-0.1766</v>
       </c>
       <c r="U7" t="n">
-        <v>0.029</v>
+        <v>0.4485</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9554</v>
+        <v>-0.1745</v>
       </c>
       <c r="W7" t="n">
-        <v>0.9554</v>
+        <v>-0.1745</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9999</v>
+        <v>-1.5518</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9</v>
+        <v>-2.3903</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9001</v>
+        <v>0.8384</v>
       </c>
       <c r="G8" t="n">
         <v>-0.294</v>
@@ -1078,13 +1078,13 @@
         <v>1.5225</v>
       </c>
       <c r="S8" t="n">
-        <v>1.014</v>
+        <v>0.4621</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7487</v>
+        <v>0.2584</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2653</v>
+        <v>0.2037</v>
       </c>
       <c r="V8" t="n">
         <v>1.3252</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1157</v>
+        <v>-1.7251</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3553</v>
+        <v>-3.2117</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7604</v>
+        <v>1.4866</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6137</v>
+        <v>-0.5046</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5292</v>
+        <v>-2.0649</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.08450000000000001</v>
+        <v>1.5602</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0182</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0182</v>
+        <v>-1.4806</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.9196</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.632</v>
+        <v>0.0564</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5475</v>
+        <v>-0.5843</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.6407</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.305</v>
+        <v>-2.6101</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.0451</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.197</v>
+        <v>-1.0905</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.6056</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1285</v>
+        <v>-0.4849</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6607</v>
+        <v>-2.0849</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.839</v>
+        <v>-1.3553</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1784</v>
+        <v>-0.7296</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.5046</v>
+        <v>-0.6137</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0649</v>
+        <v>-0.5292</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5602</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.0182</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4806</v>
+        <v>0.0182</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9196</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0564</v>
+        <v>-0.632</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5843</v>
+        <v>-0.5475</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6407</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>0.435</v>
+        <v>-1.305</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.6101</v>
+        <v>-1.305</v>
       </c>
       <c r="R10" t="n">
-        <v>3.0451</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0261</v>
+        <v>-0.1661</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2329</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7931</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8957</v>
+        <v>-2.5081</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4373</v>
+        <v>0.2009</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4584</v>
+        <v>-2.709</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7992</v>
+        <v>-0.0155</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.7422</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7992</v>
+        <v>0.7267</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6502</v>
+        <v>0.4389</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.6903</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6502</v>
+        <v>1.1292</v>
       </c>
       <c r="M11" t="n">
-        <v>0.149</v>
+        <v>-0.4543</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.0519</v>
       </c>
       <c r="O11" t="n">
-        <v>0.149</v>
+        <v>-0.4024</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-0.3203</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-0.2379</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0.0823</v>
       </c>
       <c r="V11" t="n">
         <v>-2.8249</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,58 +1345,58 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0168</v>
+        <v>-2.8957</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2461</v>
+        <v>-0.4373</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7707</v>
+        <v>-2.4584</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0155</v>
+        <v>0.7992</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.7422</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7267</v>
+        <v>0.7992</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4389</v>
+        <v>0.6502</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6903</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1292</v>
+        <v>0.6502</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4543</v>
+        <v>0.149</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0519</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4024</v>
+        <v>0.149</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6525</v>
+        <v>-0.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8289</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6850000000000001</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.144</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
         <v>-2.8249</v>
@@ -1423,31 +1423,31 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.429699999999999</v>
+        <v>-5.7447</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.4561</v>
+        <v>-12.7711</v>
       </c>
       <c r="F13" t="n">
-        <v>7.0265</v>
+        <v>7.0263</v>
       </c>
       <c r="G13" t="n">
         <v>5.0524</v>
       </c>
       <c r="H13" t="n">
-        <v>3.239699999999999</v>
+        <v>3.2397</v>
       </c>
       <c r="I13" t="n">
         <v>1.8126</v>
       </c>
       <c r="J13" t="n">
-        <v>6.539900000000001</v>
+        <v>6.539899999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>6.6632</v>
+        <v>6.663200000000002</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.1234999999999999</v>
+        <v>-0.1235000000000003</v>
       </c>
       <c r="M13" t="n">
         <v>-1.4874</v>
@@ -1459,7 +1459,7 @@
         <v>1.9361</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.087400000000001</v>
+        <v>-1.0874</v>
       </c>
       <c r="Q13" t="n">
         <v>-20.6629</v>
@@ -1468,16 +1468,16 @@
         <v>19.5756</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1151</v>
+        <v>-1.43</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.1989</v>
+        <v>-1.5139</v>
       </c>
       <c r="U13" t="n">
-        <v>0.08399999999999988</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-8.279400000000001</v>
+        <v>-8.279399999999999</v>
       </c>
       <c r="W13" t="n">
         <v>2.8663</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6077</v>
+        <v>4.756</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4531</v>
+        <v>2.4473</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1546</v>
+        <v>2.3087</v>
       </c>
       <c r="G14" t="n">
         <v>2.8968</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>1.9714</v>
+        <v>1.1197</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4132</v>
+        <v>0.4074</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5582</v>
+        <v>0.7123</v>
       </c>
       <c r="V14" t="n">
         <v>0.7395</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3431</v>
+        <v>2.5981</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4709</v>
+        <v>1.5768</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8723</v>
+        <v>1.0213</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5064</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5466</v>
+        <v>0.8015</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4937</v>
+        <v>0.5997</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0529</v>
+        <v>0.2019</v>
       </c>
       <c r="V15" t="n">
         <v>2.6504</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.7137</v>
+        <v>2.5467</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0191</v>
+        <v>0.7956</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6946</v>
+        <v>1.7511</v>
       </c>
       <c r="G16" t="n">
         <v>0.8848</v>
@@ -1702,13 +1702,13 @@
         <v>1.305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3493</v>
+        <v>0.1824</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2776</v>
+        <v>0.0541</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0717</v>
+        <v>0.1283</v>
       </c>
       <c r="V16" t="n">
         <v>0.1745</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5744</v>
+        <v>2.4358</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.2085</v>
+        <v>-0.7614</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7829</v>
+        <v>3.1972</v>
       </c>
       <c r="G17" t="n">
         <v>-2.7183</v>
@@ -1780,13 +1780,13 @@
         <v>3.2626</v>
       </c>
       <c r="S17" t="n">
-        <v>1.185</v>
+        <v>1.0464</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5564</v>
+        <v>-0.1093</v>
       </c>
       <c r="U17" t="n">
-        <v>1.7414</v>
+        <v>1.1557</v>
       </c>
       <c r="V17" t="n">
         <v>3.0202</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0371</v>
+        <v>2.2671</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0629</v>
+        <v>0.0488</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1001</v>
+        <v>2.2183</v>
       </c>
       <c r="G18" t="n">
         <v>1.4412</v>
@@ -1858,13 +1858,13 @@
         <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4916</v>
+        <v>-0.2617</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3305</v>
+        <v>-0.2187</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1612</v>
+        <v>-0.043</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.292</v>
+        <v>-0.0993</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4069</v>
+        <v>-1.1834</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1149</v>
+        <v>1.0841</v>
       </c>
       <c r="G19" t="n">
         <v>0.1305</v>
@@ -1936,13 +1936,13 @@
         <v>2.3926</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0326</v>
+        <v>0.1601</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6165</v>
+        <v>-0.3929</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5839</v>
+        <v>0.5531</v>
       </c>
       <c r="V19" t="n">
         <v>-1.695</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1976</v>
+        <v>-0.2856</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1483</v>
+        <v>-1.4778</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9507</v>
+        <v>1.1922</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6594</v>
@@ -2014,13 +2014,13 @@
         <v>2.8276</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.2554</v>
+        <v>-0.3434</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8784</v>
+        <v>-0.2079</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.377</v>
+        <v>-0.1355</v>
       </c>
       <c r="V20" t="n">
         <v>2.0647</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4292</v>
+        <v>-1.2185</v>
       </c>
       <c r="E21" t="n">
         <v>-1.5083</v>
       </c>
       <c r="F21" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.2898</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6878</v>
@@ -2092,13 +2092,13 @@
         <v>0.87</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-0.4008</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0565</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.3443</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.9929</v>
+        <v>-2.5113</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1423</v>
+        <v>-1.0306</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8506</v>
+        <v>-1.4807</v>
       </c>
       <c r="G22" t="n">
         <v>-0.2817</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.4903</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.1034</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0171</v>
+        <v>0.3869</v>
       </c>
       <c r="V22" t="n">
         <v>0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.9347</v>
+        <v>-3.3143</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.4921</v>
+        <v>-5.9333</v>
       </c>
       <c r="F23" t="n">
-        <v>2.5573</v>
+        <v>2.619</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5522</v>
@@ -2248,13 +2248,13 @@
         <v>3.0451</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5548999999999999</v>
+        <v>0.0655</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.822</v>
+        <v>-0.2632</v>
       </c>
       <c r="U23" t="n">
-        <v>0.267</v>
+        <v>0.3287</v>
       </c>
       <c r="V23" t="n">
         <v>0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.429600000000001</v>
+        <v>7.174700000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.026200000000001</v>
+        <v>-7.0263</v>
       </c>
       <c r="F24" t="n">
-        <v>13.456</v>
+        <v>14.201</v>
       </c>
       <c r="G24" t="n">
         <v>-5.0525</v>
@@ -2326,13 +2326,13 @@
         <v>20.6632</v>
       </c>
       <c r="S24" t="n">
-        <v>2.1151</v>
+        <v>2.86</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0841999999999995</v>
+        <v>-0.08390000000000025</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1991</v>
+        <v>2.9441</v>
       </c>
       <c r="V24" t="n">
         <v>8.279500000000001</v>
